--- a/V.1.4/Project Outputs for DONGLE01/Generate Files/BOM/Bill of Materials Tech-DONGLE01.xlsx
+++ b/V.1.4/Project Outputs for DONGLE01/Generate Files/BOM/Bill of Materials Tech-DONGLE01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PCB\PRJ_Dongle01\Project Outputs for DONGLE01\Generate Files\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PCB\PRJ_Dongle01\V.1.4\Project Outputs for DONGLE01\Generate Files\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8176E4E-D490-4322-9FB4-1355A9FC58CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB7401D3-5FB8-469A-9B5D-E3C908C7EC45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{BFA44F07-169C-4D10-99F9-CCE2C054F9B8}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11505" xr2:uid="{31663E7A-10DD-4289-A5C7-1DEB43947972}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials Tech-DONGLE01" sheetId="1" r:id="rId1"/>
@@ -869,7 +869,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61647F3A-2EC3-4AB2-A00F-ED5CDEA75A90}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{856090A4-C49C-46B3-8B65-1EBCE3D8FD18}">
   <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1429,6 +1429,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
 </file>
--- a/V.1.4/Project Outputs for DONGLE01/Generate Files/BOM/Bill of Materials Tech-DONGLE01.xlsx
+++ b/V.1.4/Project Outputs for DONGLE01/Generate Files/BOM/Bill of Materials Tech-DONGLE01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PCB\PRJ_Dongle01\V.1.4\Project Outputs for DONGLE01\Generate Files\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB7401D3-5FB8-469A-9B5D-E3C908C7EC45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1B8850A-BDB8-40D8-A961-9712C91DCC19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11505" xr2:uid="{31663E7A-10DD-4289-A5C7-1DEB43947972}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{9C138E72-95A8-4333-9204-BE466A6086E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials Tech-DONGLE01" sheetId="1" r:id="rId1"/>
@@ -869,7 +869,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{856090A4-C49C-46B3-8B65-1EBCE3D8FD18}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E3F2C40-7870-4FD7-AEF9-2ED1B2F3E3A3}">
   <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/V.1.4/Project Outputs for DONGLE01/Generate Files/BOM/Bill of Materials Tech-DONGLE01.xlsx
+++ b/V.1.4/Project Outputs for DONGLE01/Generate Files/BOM/Bill of Materials Tech-DONGLE01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PCB\PRJ_Dongle01\V.1.4\Project Outputs for DONGLE01\Generate Files\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1B8850A-BDB8-40D8-A961-9712C91DCC19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E1785CE-D2B3-44E2-9D2F-6A11303DED81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{9C138E72-95A8-4333-9204-BE466A6086E5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{15357146-2741-4B2C-B584-BDF5BF96D88B}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials Tech-DONGLE01" sheetId="1" r:id="rId1"/>
@@ -869,7 +869,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E3F2C40-7870-4FD7-AEF9-2ED1B2F3E3A3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BD6001F-3034-4E04-AC50-A110B6066ED6}">
   <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1429,6 +1429,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>